--- a/data/sample_input.xlsx
+++ b/data/sample_input.xlsx
@@ -1145,7 +1145,7 @@
         <v>46183</v>
       </c>
       <c r="G2" s="3">
-        <v>46183.5</v>
+        <v>46183.2916666667</v>
       </c>
     </row>
   </sheetData>

--- a/data/sample_input.xlsx
+++ b/data/sample_input.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11400"/>
+    <workbookView windowWidth="28800" windowHeight="11400" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="01排产信息（输入）" sheetId="1" r:id="rId1"/>
@@ -1259,7 +1259,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/data/sample_input.xlsx
+++ b/data/sample_input.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11400" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="11400" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01排产信息（输入）" sheetId="1" r:id="rId1"/>
-    <sheet name="02输入（SR拆分）" sheetId="2" r:id="rId2"/>
+    <sheet name="01排产信息 (输入)" sheetId="1" r:id="rId1"/>
+    <sheet name="02输入 (SR拆分)" sheetId="2" r:id="rId2"/>
     <sheet name="03包规基表" sheetId="3" r:id="rId3"/>
     <sheet name="04供应商作息&amp;车规基表" sheetId="4" r:id="rId4"/>
   </sheets>
